--- a/переводы-13.5/08 Breaking Bad.xlsx
+++ b/переводы-13.5/08 Breaking Bad.xlsx
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Я тот, кто к нему стучит.</t>
+          <t>Я тот, кто стучится к нему в дверь.</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Меня тошнит слушать этого мудака.</t>
+          <t>Меня уже тошнит слушать этого мудака.</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>для заданий</t>
+          <t>пассивная (только понять)</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -2985,11 +2985,7 @@
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>ссоры</t>
-        </is>
-      </c>
+      <c r="S22" s="3" t="inlineStr"/>
       <c r="T22" s="3" t="inlineStr">
         <is>
           <t>18.6–19.7</t>
@@ -9372,7 +9368,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Я тот, кто к нему стучит.</t>
+          <t>Я тот, кто стучится к нему в дверь.</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -9540,7 +9536,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Дать ему сказать? Меня тошнит слушать этого мудака.</t>
+          <t>Дать ему сказать? Меня уже тошнит слушать этого мудака.</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -11425,7 +11421,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Ja. Ihnen auch.</t>
+          <t>Ja. Ihnen noch.</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
